--- a/New_Outputs/between_drug_comparison/Stats_Between_Drug_Comparison.xlsx
+++ b/New_Outputs/between_drug_comparison/Stats_Between_Drug_Comparison.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="153">
   <si>
     <t>group</t>
   </si>
@@ -76,7 +76,7 @@
     <t>Intercept</t>
   </si>
   <si>
-    <t>6.2e-04</t>
+    <t>&lt;10⁻⁵</t>
   </si>
   <si>
     <t>group_TvsH</t>
@@ -85,7 +85,7 @@
     <t>Drug group (Tramadol vs Hydrocodone)</t>
   </si>
   <si>
-    <t>0.783</t>
+    <t>0.437</t>
   </si>
   <si>
     <t>log_ROE</t>
@@ -94,7 +94,7 @@
     <t>log10 ROE</t>
   </si>
   <si>
-    <t>0.462</t>
+    <t>0.428</t>
   </si>
   <si>
     <t>R_5HT4</t>
@@ -103,7 +103,7 @@
     <t>5-HT4 activity</t>
   </si>
   <si>
-    <t>0.167</t>
+    <t>0.135</t>
   </si>
   <si>
     <t>R_5HT6</t>
@@ -112,7 +112,7 @@
     <t>5-HT6 activity</t>
   </si>
   <si>
-    <t>0.156</t>
+    <t>0.393</t>
   </si>
   <si>
     <t>Pooled_grpint</t>
@@ -121,19 +121,16 @@
     <t>5-HT4 + 5-HT6 + ROE + drug + drug x each predictor</t>
   </si>
   <si>
-    <t>&lt;10⁻⁵</t>
-  </si>
-  <si>
-    <t>7.2e-04</t>
-  </si>
-  <si>
-    <t>0.028</t>
-  </si>
-  <si>
-    <t>0.007</t>
-  </si>
-  <si>
-    <t>0.646</t>
+    <t>0.715</t>
+  </si>
+  <si>
+    <t>0.657</t>
+  </si>
+  <si>
+    <t>0.016</t>
+  </si>
+  <si>
+    <t>0.558</t>
   </si>
   <si>
     <t>group_x_logROE</t>
@@ -142,7 +139,7 @@
     <t>Group x log10 ROE</t>
   </si>
   <si>
-    <t>3.5e-04</t>
+    <t>0.812</t>
   </si>
   <si>
     <t>group_x_5HT4</t>
@@ -151,7 +148,7 @@
     <t>Group x 5-HT4</t>
   </si>
   <si>
-    <t>0.018</t>
+    <t>0.034</t>
   </si>
   <si>
     <t>group_x_5HT6</t>
@@ -160,7 +157,7 @@
     <t>Group x 5-HT6</t>
   </si>
   <si>
-    <t>0.015</t>
+    <t>0.036</t>
   </si>
   <si>
     <t>formula</t>
@@ -238,7 +235,7 @@
     <t>drug x each predictor</t>
   </si>
   <si>
-    <t>3.3e-04</t>
+    <t>0.105</t>
   </si>
   <si>
     <t>predictor</t>
@@ -253,13 +250,13 @@
     <t>Tramadol group</t>
   </si>
   <si>
-    <t>0.002</t>
-  </si>
-  <si>
-    <t>0.370</t>
-  </si>
-  <si>
-    <t>0.001</t>
+    <t>0.577</t>
+  </si>
+  <si>
+    <t>0.425</t>
+  </si>
+  <si>
+    <t>0.026</t>
   </si>
   <si>
     <t>comparison</t>
@@ -280,16 +277,13 @@
     <t>ROE + 5-HT4</t>
   </si>
   <si>
-    <t>0.006</t>
-  </si>
-  <si>
     <t>.grpTramadol group:R_5HT4</t>
   </si>
   <si>
     <t>5HT4</t>
   </si>
   <si>
-    <t>0.205</t>
+    <t>0.230</t>
   </si>
   <si>
     <t>HT6</t>
@@ -298,7 +292,7 @@
     <t>ROE + 5-HT6</t>
   </si>
   <si>
-    <t>5.8e-04</t>
+    <t>0.982</t>
   </si>
   <si>
     <t>.grpTramadol group:R_5HT6</t>
@@ -307,7 +301,7 @@
     <t>5HT6</t>
   </si>
   <si>
-    <t>0.101</t>
+    <t>0.185</t>
   </si>
   <si>
     <t>HT4_HT6</t>
@@ -322,13 +316,13 @@
     <t>ROE + 5-HT4 + 5-HT6 + ROEx5-HT4 + ROEx5-HT6</t>
   </si>
   <si>
-    <t>0.137</t>
-  </si>
-  <si>
-    <t>0.881</t>
-  </si>
-  <si>
-    <t>0.289</t>
+    <t>0.326</t>
+  </si>
+  <si>
+    <t>0.331</t>
+  </si>
+  <si>
+    <t>0.345</t>
   </si>
   <si>
     <t>.grpTramadol group:R_5HT4_x_ROE</t>
@@ -340,7 +334,7 @@
     <t>5-HT4 x log10 ROE</t>
   </si>
   <si>
-    <t>0.766</t>
+    <t>0.465</t>
   </si>
   <si>
     <t>.grpTramadol group:R_5HT6_x_ROE</t>
@@ -352,7 +346,7 @@
     <t>5-HT6 x log10 ROE</t>
   </si>
   <si>
-    <t>0.366</t>
+    <t>0.580</t>
   </si>
   <si>
     <t>HT4_HT6_ROEint_Cov</t>
@@ -361,19 +355,19 @@
     <t>ROE + 5-HT4 + 5-HT6 + ROEx5-HT4 + ROEx5-HT6 + Sex + log MME + MQS non-opioid</t>
   </si>
   <si>
-    <t>0.502</t>
-  </si>
-  <si>
-    <t>0.979</t>
-  </si>
-  <si>
-    <t>0.314</t>
-  </si>
-  <si>
-    <t>0.847</t>
-  </si>
-  <si>
-    <t>0.368</t>
+    <t>0.742</t>
+  </si>
+  <si>
+    <t>0.513</t>
+  </si>
+  <si>
+    <t>0.401</t>
+  </si>
+  <si>
+    <t>0.629</t>
+  </si>
+  <si>
+    <t>0.681</t>
   </si>
   <si>
     <t>.grpTramadol group:sex_female</t>
@@ -385,7 +379,7 @@
     <t>Sex (female)</t>
   </si>
   <si>
-    <t>0.868</t>
+    <t>0.809</t>
   </si>
   <si>
     <t>.grpTramadol group:log_MME</t>
@@ -397,7 +391,7 @@
     <t>log10 MME</t>
   </si>
   <si>
-    <t>0.791</t>
+    <t>0.605</t>
   </si>
   <si>
     <t>.grpTramadol group:MQS_nonopioid</t>
@@ -409,10 +403,19 @@
     <t>MQS non-opioid</t>
   </si>
   <si>
-    <t>0.386</t>
-  </si>
-  <si>
-    <t>0.023</t>
+    <t>0.653</t>
+  </si>
+  <si>
+    <t>0.475</t>
+  </si>
+  <si>
+    <t>0.408</t>
+  </si>
+  <si>
+    <t>0.189</t>
+  </si>
+  <si>
+    <t>0.246</t>
   </si>
   <si>
     <t>setting</t>
@@ -879,25 +882,25 @@
         <v>17</v>
       </c>
       <c r="F2">
-        <v>7.767977117480115</v>
+        <v>6.924819194814973</v>
       </c>
       <c r="G2">
-        <v>2.040037152161492</v>
+        <v>0.9466056746496521</v>
       </c>
       <c r="H2">
-        <v>3.807762573955904</v>
+        <v>7.315421173001013</v>
       </c>
       <c r="I2">
-        <v>0.0006214258751689964</v>
+        <v>7.937075367250976E-09</v>
       </c>
       <c r="J2" t="s">
         <v>18</v>
       </c>
       <c r="K2">
-        <v>3.607293914498516</v>
+        <v>5.01012849184585</v>
       </c>
       <c r="L2">
-        <v>11.92866032046171</v>
+        <v>8.839509897784097</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -917,28 +920,28 @@
         <v>20</v>
       </c>
       <c r="F3">
-        <v>0.3366150136245711</v>
+        <v>-0.6103441243220943</v>
       </c>
       <c r="G3">
-        <v>1.213526298173313</v>
+        <v>0.776868417553272</v>
       </c>
       <c r="H3">
-        <v>0.2773858416840806</v>
+        <v>-0.7856467202571552</v>
       </c>
       <c r="I3">
-        <v>0.7833253069498571</v>
+        <v>0.4368217875159957</v>
       </c>
       <c r="J3" t="s">
         <v>21</v>
       </c>
       <c r="K3">
-        <v>-2.138388189055558</v>
+        <v>-2.181708818570424</v>
       </c>
       <c r="L3">
-        <v>2.8116182163047</v>
+        <v>0.9610205699262356</v>
       </c>
       <c r="M3">
-        <v>2.93677143338298</v>
+        <v>1.512514587251137</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -958,28 +961,28 @@
         <v>23</v>
       </c>
       <c r="F4">
-        <v>0.5345780090011439</v>
+        <v>0.1992636041772622</v>
       </c>
       <c r="G4">
-        <v>0.71743227324081</v>
+        <v>0.2485644901132651</v>
       </c>
       <c r="H4">
-        <v>0.7451267930648415</v>
+        <v>0.8016575661570257</v>
       </c>
       <c r="I4">
-        <v>0.4618073755497951</v>
+        <v>0.4276086972360122</v>
       </c>
       <c r="J4" t="s">
         <v>24</v>
       </c>
       <c r="K4">
-        <v>-0.9286347591522303</v>
+        <v>-0.3035055330184062</v>
       </c>
       <c r="L4">
-        <v>1.997790777154518</v>
+        <v>0.7020327413729306</v>
       </c>
       <c r="M4">
-        <v>2.579134161102549</v>
+        <v>1.194538713827082</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -999,28 +1002,28 @@
         <v>26</v>
       </c>
       <c r="F5">
-        <v>1.23294535434831</v>
+        <v>1.286807494181932</v>
       </c>
       <c r="G5">
-        <v>0.8716844588368344</v>
+        <v>0.8439177379255773</v>
       </c>
       <c r="H5">
-        <v>1.414439986682266</v>
+        <v>1.524802046873687</v>
       </c>
       <c r="I5">
-        <v>0.1671987350586183</v>
+        <v>0.13537764926237</v>
       </c>
       <c r="J5" t="s">
         <v>27</v>
       </c>
       <c r="K5">
-        <v>-0.54486682046419</v>
+        <v>-0.4201772515780959</v>
       </c>
       <c r="L5">
-        <v>3.01075752916081</v>
+        <v>2.99379223994196</v>
       </c>
       <c r="M5">
-        <v>1.207936378372018</v>
+        <v>1.293919161254231</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1040,28 +1043,28 @@
         <v>29</v>
       </c>
       <c r="F6">
-        <v>1.937806399935482</v>
+        <v>1.015136764549823</v>
       </c>
       <c r="G6">
-        <v>1.333842046272818</v>
+        <v>1.174949817559821</v>
       </c>
       <c r="H6">
-        <v>1.452800506139639</v>
+        <v>0.8639830819822556</v>
       </c>
       <c r="I6">
-        <v>0.1563272750189022</v>
+        <v>0.3928800335087943</v>
       </c>
       <c r="J6" t="s">
         <v>30</v>
       </c>
       <c r="K6">
-        <v>-0.78258238880683</v>
+        <v>-1.361423562927276</v>
       </c>
       <c r="L6">
-        <v>4.658195188677794</v>
+        <v>3.391697092026923</v>
       </c>
       <c r="M6">
-        <v>1.312637484062222</v>
+        <v>1.414581534235803</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1081,25 +1084,25 @@
         <v>17</v>
       </c>
       <c r="F7">
-        <v>10.23828795713792</v>
+        <v>6.712546745977006</v>
       </c>
       <c r="G7">
-        <v>1.725204440827802</v>
+        <v>1.046377247201655</v>
       </c>
       <c r="H7">
-        <v>5.934536055463256</v>
+        <v>6.415035078341473</v>
       </c>
       <c r="I7">
-        <v>2.182828046530215E-06</v>
+        <v>1.944785221407309E-07</v>
       </c>
       <c r="J7" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="K7">
-        <v>6.704366859489374</v>
+        <v>4.590395328164892</v>
       </c>
       <c r="L7">
-        <v>13.77220905478646</v>
+        <v>8.83469816378912</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1119,28 +1122,28 @@
         <v>20</v>
       </c>
       <c r="F8">
-        <v>-20.42973546705934</v>
+        <v>0.860022368175224</v>
       </c>
       <c r="G8">
-        <v>5.378314243481985</v>
+        <v>2.33344327803749</v>
       </c>
       <c r="H8">
-        <v>-3.798538825026499</v>
+        <v>0.3685636485231104</v>
       </c>
       <c r="I8">
-        <v>0.0007192790821064997</v>
+        <v>0.7146116232855019</v>
       </c>
       <c r="J8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K8">
-        <v>-31.44671277422693</v>
+        <v>-3.872419945640766</v>
       </c>
       <c r="L8">
-        <v>-9.412758159891759</v>
+        <v>5.592464681991214</v>
       </c>
       <c r="M8">
-        <v>100.1087420740921</v>
+        <v>14.90679017792069</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1160,28 +1163,28 @@
         <v>23</v>
       </c>
       <c r="F9">
-        <v>1.411945101876967</v>
+        <v>0.1261341214908756</v>
       </c>
       <c r="G9">
-        <v>0.6080394105697842</v>
+        <v>0.2816800054615264</v>
       </c>
       <c r="H9">
-        <v>2.322127607738214</v>
+        <v>0.4477922431313776</v>
       </c>
       <c r="I9">
-        <v>0.02772005524695164</v>
+        <v>0.6569863198334958</v>
       </c>
       <c r="J9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K9">
-        <v>0.1664328307728498</v>
+        <v>-0.4451394077817867</v>
       </c>
       <c r="L9">
-        <v>2.657457372981083</v>
+        <v>0.6974076507635378</v>
       </c>
       <c r="M9">
-        <v>3.215018444033927</v>
+        <v>1.675788098265167</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1201,28 +1204,28 @@
         <v>26</v>
       </c>
       <c r="F10">
-        <v>2.463101544153734</v>
+        <v>2.617184130207268</v>
       </c>
       <c r="G10">
-        <v>0.8532700296459648</v>
+        <v>1.033244507224722</v>
       </c>
       <c r="H10">
-        <v>2.886661266159452</v>
+        <v>2.532976572251018</v>
       </c>
       <c r="I10">
-        <v>0.007420647090409472</v>
+        <v>0.01580975817710643</v>
       </c>
       <c r="J10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K10">
-        <v>0.7152571215470993</v>
+        <v>0.5216671435588078</v>
       </c>
       <c r="L10">
-        <v>4.210945966760368</v>
+        <v>4.712701116855728</v>
       </c>
       <c r="M10">
-        <v>2.008659544536179</v>
+        <v>2.118839821979326</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1242,28 +1245,28 @@
         <v>29</v>
       </c>
       <c r="F11">
-        <v>0.6022133601106122</v>
+        <v>-0.8663007856997327</v>
       </c>
       <c r="G11">
-        <v>1.295567046531564</v>
+        <v>1.465053125070908</v>
       </c>
       <c r="H11">
-        <v>0.464826086556332</v>
+        <v>-0.5913101517447049</v>
       </c>
       <c r="I11">
-        <v>0.6456505755500963</v>
+        <v>0.5580075557670632</v>
       </c>
       <c r="J11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K11">
-        <v>-2.051635430679216</v>
+        <v>-3.837566239773702</v>
       </c>
       <c r="L11">
-        <v>3.256062150900441</v>
+        <v>2.104964668374237</v>
       </c>
       <c r="M11">
-        <v>2.149134895009506</v>
+        <v>2.402597920554649</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1277,34 +1280,34 @@
         <v>32</v>
       </c>
       <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
         <v>38</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12">
+        <v>0.1268338083727644</v>
+      </c>
+      <c r="G12">
+        <v>0.5299594151679201</v>
+      </c>
+      <c r="H12">
+        <v>0.2393273989340797</v>
+      </c>
+      <c r="I12">
+        <v>0.8122090832102913</v>
+      </c>
+      <c r="J12" t="s">
         <v>39</v>
       </c>
-      <c r="F12">
-        <v>-5.778734418070625</v>
-      </c>
-      <c r="G12">
-        <v>1.421121084661567</v>
-      </c>
-      <c r="H12">
-        <v>-4.066320935240223</v>
-      </c>
-      <c r="I12">
-        <v>0.000351662226711714</v>
-      </c>
-      <c r="J12" t="s">
-        <v>40</v>
-      </c>
       <c r="K12">
-        <v>-8.689768997247185</v>
+        <v>-0.9479737022924025</v>
       </c>
       <c r="L12">
-        <v>-2.867699838894066</v>
+        <v>1.201641319037931</v>
       </c>
       <c r="M12">
-        <v>113.2453607231068</v>
+        <v>16.78397355412313</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1318,34 +1321,34 @@
         <v>32</v>
       </c>
       <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
         <v>41</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13">
+        <v>-3.668812566895016</v>
+      </c>
+      <c r="G13">
+        <v>1.664098184615456</v>
+      </c>
+      <c r="H13">
+        <v>-2.204685156689126</v>
+      </c>
+      <c r="I13">
+        <v>0.03395187436829785</v>
+      </c>
+      <c r="J13" t="s">
         <v>42</v>
       </c>
-      <c r="F13">
-        <v>-3.424236830192158</v>
-      </c>
-      <c r="G13">
-        <v>1.356763227019878</v>
-      </c>
-      <c r="H13">
-        <v>-2.523827858832431</v>
-      </c>
-      <c r="I13">
-        <v>0.01756138370750144</v>
-      </c>
-      <c r="J13" t="s">
-        <v>43</v>
-      </c>
       <c r="K13">
-        <v>-6.203440314144839</v>
+        <v>-7.043760112156079</v>
       </c>
       <c r="L13">
-        <v>-0.6450333462394773</v>
+        <v>-0.2938650216339522</v>
       </c>
       <c r="M13">
-        <v>2.079549529930505</v>
+        <v>2.298300962095085</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1359,34 +1362,34 @@
         <v>32</v>
       </c>
       <c r="D14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" t="s">
         <v>44</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14">
+        <v>5.031241254276178</v>
+      </c>
+      <c r="G14">
+        <v>2.31481099839796</v>
+      </c>
+      <c r="H14">
+        <v>2.173499805279226</v>
+      </c>
+      <c r="I14">
+        <v>0.03640018383724646</v>
+      </c>
+      <c r="J14" t="s">
         <v>45</v>
       </c>
-      <c r="F14">
-        <v>5.501499320232195</v>
-      </c>
-      <c r="G14">
-        <v>2.121023700020244</v>
-      </c>
-      <c r="H14">
-        <v>2.59379436457013</v>
-      </c>
-      <c r="I14">
-        <v>0.01493073044433937</v>
-      </c>
-      <c r="J14" t="s">
-        <v>46</v>
-      </c>
       <c r="K14">
-        <v>1.156779225193753</v>
+        <v>0.3365869550217075</v>
       </c>
       <c r="L14">
-        <v>9.846219415270639</v>
+        <v>9.725895553530648</v>
       </c>
       <c r="M14">
-        <v>3.354066065917745</v>
+        <v>3.716590790767547</v>
       </c>
     </row>
   </sheetData>
@@ -1407,55 +1410,55 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:19">
@@ -1466,55 +1469,55 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E2">
         <v>4</v>
       </c>
       <c r="F2">
-        <v>0.201871592887501</v>
+        <v>0.1733005069932461</v>
       </c>
       <c r="G2">
-        <v>0.09888728229233978</v>
+        <v>0.08851081540280969</v>
       </c>
       <c r="H2">
-        <v>1.960216966262686</v>
+        <v>2.043886511940011</v>
       </c>
       <c r="I2">
         <v>4</v>
       </c>
       <c r="J2">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="K2">
-        <v>0.1253065620644413</v>
+        <v>0.1070755283712192</v>
       </c>
       <c r="L2">
-        <v>2.121114581800357</v>
+        <v>2.092882793188412</v>
       </c>
       <c r="M2">
-        <v>1.968311029671189</v>
+        <v>1.970384001885171</v>
       </c>
       <c r="N2">
-        <v>162.9202341273081</v>
+        <v>196.5506943961124</v>
       </c>
       <c r="O2">
-        <v>172.4213477580448</v>
+        <v>207.255832199622</v>
       </c>
       <c r="P2">
-        <v>2.93677143338298</v>
+        <v>1.512514587251137</v>
       </c>
       <c r="Q2">
-        <v>0.1475134424922531</v>
+        <v>0.2641909736342764</v>
       </c>
       <c r="R2">
-        <v>0.3270018724807287</v>
+        <v>0.5720382584080176</v>
       </c>
       <c r="S2">
-        <v>0.3953376693865056</v>
+        <v>0.599810131901279</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1525,55 +1528,55 @@
         <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E3">
         <v>7</v>
       </c>
       <c r="F3">
-        <v>0.5846050511030607</v>
+        <v>0.3014450688406731</v>
       </c>
       <c r="G3">
-        <v>0.4807563138788259</v>
+        <v>0.1656149433374707</v>
       </c>
       <c r="H3">
-        <v>5.629390079541896</v>
+        <v>2.219279911020667</v>
       </c>
       <c r="I3">
         <v>7</v>
       </c>
       <c r="J3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="K3">
-        <v>0.0003962800662822457</v>
+        <v>0.05547850374735885</v>
       </c>
       <c r="L3">
-        <v>1.610127183527307</v>
+        <v>2.002407237239812</v>
       </c>
       <c r="M3">
-        <v>1.419998702266036</v>
+        <v>1.811245495477262</v>
       </c>
       <c r="N3">
-        <v>145.4108033462592</v>
+        <v>195.1398869579028</v>
       </c>
       <c r="O3">
-        <v>159.6624737923642</v>
+        <v>211.1975936631672</v>
       </c>
       <c r="P3">
-        <v>113.2453607231068</v>
+        <v>16.78397355412313</v>
       </c>
       <c r="Q3">
-        <v>0.2031015730703495</v>
+        <v>0.3089547863532224</v>
       </c>
       <c r="R3">
-        <v>0.2488819023011641</v>
+        <v>0.6513680142561976</v>
       </c>
       <c r="S3">
-        <v>0.8265856038332907</v>
+        <v>0.5598606966497767</v>
       </c>
     </row>
   </sheetData>
@@ -1588,25 +1591,25 @@
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>8</v>
@@ -1623,25 +1626,25 @@
         <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>8.599476119849234</v>
+        <v>2.201308263069723</v>
       </c>
       <c r="H2">
-        <v>0.0003324260727056167</v>
+        <v>0.1047438292094812</v>
       </c>
       <c r="I2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1656,10 +1659,10 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1694,28 +1697,28 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2">
-        <v>1.411945101876967</v>
+        <v>0.1261341214908756</v>
       </c>
       <c r="E2">
-        <v>0.6080394105697842</v>
+        <v>0.2816800054615264</v>
       </c>
       <c r="F2">
-        <v>0.1664328307728498</v>
+        <v>-0.4451394077817867</v>
       </c>
       <c r="G2">
-        <v>2.657457372981083</v>
+        <v>0.6974076507635378</v>
       </c>
       <c r="H2">
-        <v>2.322127607738214</v>
+        <v>0.4477922431313777</v>
       </c>
       <c r="I2">
-        <v>0.02772005524695164</v>
+        <v>0.6569863198334958</v>
       </c>
       <c r="J2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1726,28 +1729,28 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3">
+        <v>0.25296792986364</v>
+      </c>
+      <c r="E3">
+        <v>0.4489023905575894</v>
+      </c>
+      <c r="F3">
+        <v>-0.6574483154519903</v>
+      </c>
+      <c r="G3">
+        <v>1.16338417517927</v>
+      </c>
+      <c r="H3">
+        <v>0.5635254683082088</v>
+      </c>
+      <c r="I3">
+        <v>0.5765707560804818</v>
+      </c>
+      <c r="J3" t="s">
         <v>76</v>
-      </c>
-      <c r="D3">
-        <v>-4.366789316193659</v>
-      </c>
-      <c r="E3">
-        <v>1.284473904936811</v>
-      </c>
-      <c r="F3">
-        <v>-6.997914836515848</v>
-      </c>
-      <c r="G3">
-        <v>-1.735663795871468</v>
-      </c>
-      <c r="H3">
-        <v>-3.399671491503348</v>
-      </c>
-      <c r="I3">
-        <v>0.002044258222353747</v>
-      </c>
-      <c r="J3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1758,28 +1761,28 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D4">
-        <v>2.463101544153734</v>
+        <v>2.617184130207268</v>
       </c>
       <c r="E4">
-        <v>0.8532700296459648</v>
+        <v>1.033244507224722</v>
       </c>
       <c r="F4">
-        <v>0.7152571215470993</v>
+        <v>0.5216671435588078</v>
       </c>
       <c r="G4">
-        <v>4.210945966760368</v>
+        <v>4.712701116855728</v>
       </c>
       <c r="H4">
-        <v>2.886661266159452</v>
+        <v>2.532976572251018</v>
       </c>
       <c r="I4">
-        <v>0.007420647090409472</v>
+        <v>0.01580975817710643</v>
       </c>
       <c r="J4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1790,28 +1793,28 @@
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D5">
-        <v>-0.9611352860384246</v>
+        <v>-1.051628436687748</v>
       </c>
       <c r="E5">
-        <v>1.054863361152224</v>
+        <v>1.304464854386808</v>
       </c>
       <c r="F5">
-        <v>-3.121924928640777</v>
+        <v>-3.69720578235947</v>
       </c>
       <c r="G5">
-        <v>1.199654356563928</v>
+        <v>1.593948908983974</v>
       </c>
       <c r="H5">
-        <v>-0.911146714763682</v>
+        <v>-0.8061761366365739</v>
       </c>
       <c r="I5">
-        <v>0.3699959931810703</v>
+        <v>0.4254349377076269</v>
       </c>
       <c r="J5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1822,28 +1825,28 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D6">
-        <v>0.6022133601106122</v>
+        <v>-0.8663007856997327</v>
       </c>
       <c r="E6">
-        <v>1.295567046531564</v>
+        <v>1.465053125070908</v>
       </c>
       <c r="F6">
-        <v>-2.051635430679216</v>
+        <v>-3.837566239773702</v>
       </c>
       <c r="G6">
-        <v>3.256062150900441</v>
+        <v>2.104964668374237</v>
       </c>
       <c r="H6">
-        <v>0.464826086556332</v>
+        <v>-0.591310151744705</v>
       </c>
       <c r="I6">
-        <v>0.6456505755500963</v>
+        <v>0.558007555767063</v>
       </c>
       <c r="J6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1854,28 +1857,28 @@
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D7">
-        <v>6.103712680342808</v>
+        <v>4.164940468576446</v>
       </c>
       <c r="E7">
-        <v>1.679359271862053</v>
+        <v>1.792196780218101</v>
       </c>
       <c r="F7">
-        <v>2.663701154220517</v>
+        <v>0.5301969300396356</v>
       </c>
       <c r="G7">
-        <v>9.543724206465098</v>
+        <v>7.799684007113256</v>
       </c>
       <c r="H7">
-        <v>3.634548474892503</v>
+        <v>2.323930337643835</v>
       </c>
       <c r="I7">
-        <v>0.001109057267382744</v>
+        <v>0.02588905186811915</v>
       </c>
       <c r="J7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1896,13 +1899,13 @@
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -1929,7 +1932,7 @@
         <v>4</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>9</v>
@@ -1937,369 +1940,369 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" t="s">
         <v>82</v>
-      </c>
-      <c r="B2" t="s">
-        <v>83</v>
       </c>
       <c r="C2" t="s">
         <v>22</v>
       </c>
       <c r="D2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2">
+        <v>44</v>
+      </c>
+      <c r="F2">
+        <v>0.2037659297921492</v>
+      </c>
+      <c r="G2">
+        <v>0.5534642477211291</v>
+      </c>
+      <c r="H2">
+        <v>0.3681645754556843</v>
+      </c>
+      <c r="I2">
+        <v>0.7147935384294545</v>
+      </c>
+      <c r="J2">
+        <v>-0.9166638632284333</v>
+      </c>
+      <c r="K2">
+        <v>1.324195722812732</v>
+      </c>
+      <c r="L2" t="s">
         <v>84</v>
-      </c>
-      <c r="E2">
-        <v>36</v>
-      </c>
-      <c r="F2">
-        <v>-4.887134700262774</v>
-      </c>
-      <c r="G2">
-        <v>1.644367348188758</v>
-      </c>
-      <c r="H2">
-        <v>-2.972045574637484</v>
-      </c>
-      <c r="I2">
-        <v>0.005781869300953446</v>
-      </c>
-      <c r="J2">
-        <v>-8.245380843509782</v>
-      </c>
-      <c r="K2">
-        <v>-1.528888557015765</v>
-      </c>
-      <c r="L2" t="s">
-        <v>85</v>
       </c>
       <c r="M2" t="s">
         <v>23</v>
       </c>
       <c r="N2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
         <v>25</v>
       </c>
       <c r="D3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3">
+        <v>44</v>
+      </c>
+      <c r="F3">
+        <v>-1.888274272827088</v>
+      </c>
+      <c r="G3">
+        <v>1.547763861027437</v>
+      </c>
+      <c r="H3">
+        <v>-1.220001526313977</v>
+      </c>
+      <c r="I3">
+        <v>0.2299819576901632</v>
+      </c>
+      <c r="J3">
+        <v>-5.021558400204889</v>
+      </c>
+      <c r="K3">
+        <v>1.245009854550712</v>
+      </c>
+      <c r="L3" t="s">
         <v>84</v>
       </c>
-      <c r="E3">
-        <v>36</v>
-      </c>
-      <c r="F3">
-        <v>-1.906542506110529</v>
-      </c>
-      <c r="G3">
-        <v>1.470318719242319</v>
-      </c>
-      <c r="H3">
-        <v>-1.296686549085768</v>
-      </c>
-      <c r="I3">
-        <v>0.2046245320982059</v>
-      </c>
-      <c r="J3">
-        <v>-4.909333928403231</v>
-      </c>
-      <c r="K3">
-        <v>1.096248916182172</v>
-      </c>
-      <c r="L3" t="s">
-        <v>85</v>
-      </c>
       <c r="M3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
         <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E4">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F4">
-        <v>-6.071416259789797</v>
+        <v>-0.01293393813719212</v>
       </c>
       <c r="G4">
-        <v>1.577859503894293</v>
+        <v>0.5600062553314245</v>
       </c>
       <c r="H4">
-        <v>-3.847881414539773</v>
+        <v>-0.02309606011371697</v>
       </c>
       <c r="I4">
-        <v>0.00057900884939516</v>
+        <v>0.9816945054523754</v>
       </c>
       <c r="J4">
-        <v>-9.293835264506248</v>
+        <v>-1.146607333184324</v>
       </c>
       <c r="K4">
-        <v>-2.848997255073346</v>
+        <v>1.12073945690994</v>
       </c>
       <c r="L4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M4" t="s">
         <v>23</v>
       </c>
       <c r="N4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
         <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F5">
-        <v>3.676698186670552</v>
+        <v>2.955447532808183</v>
       </c>
       <c r="G5">
-        <v>2.174611148707129</v>
+        <v>2.189494208477956</v>
       </c>
       <c r="H5">
-        <v>1.690738221799542</v>
+        <v>1.349831171676259</v>
       </c>
       <c r="I5">
-        <v>0.1012525841897636</v>
+        <v>0.1850566507622613</v>
       </c>
       <c r="J5">
-        <v>-0.7644502654996144</v>
+        <v>-1.476951764753649</v>
       </c>
       <c r="K5">
-        <v>8.117846638840717</v>
+        <v>7.387846830370014</v>
       </c>
       <c r="L5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E6">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F6">
-        <v>-5.778734418070625</v>
+        <v>0.1268338083727644</v>
       </c>
       <c r="G6">
-        <v>1.421121084661567</v>
+        <v>0.5299594151679201</v>
       </c>
       <c r="H6">
-        <v>-4.066320935240223</v>
+        <v>0.2393273989340797</v>
       </c>
       <c r="I6">
-        <v>0.000351662226711714</v>
+        <v>0.8122090832102913</v>
       </c>
       <c r="J6">
-        <v>-8.689768997247185</v>
+        <v>-0.9479737022924025</v>
       </c>
       <c r="K6">
-        <v>-2.867699838894066</v>
+        <v>1.201641319037931</v>
       </c>
       <c r="L6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M6" t="s">
         <v>23</v>
       </c>
       <c r="N6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
         <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E7">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F7">
-        <v>-3.424236830192158</v>
+        <v>-3.668812566895016</v>
       </c>
       <c r="G7">
-        <v>1.356763227019878</v>
+        <v>1.664098184615456</v>
       </c>
       <c r="H7">
-        <v>-2.523827858832431</v>
+        <v>-2.204685156689126</v>
       </c>
       <c r="I7">
-        <v>0.01756138370750144</v>
+        <v>0.03395187436829785</v>
       </c>
       <c r="J7">
-        <v>-6.203440314144839</v>
+        <v>-7.043760112156079</v>
       </c>
       <c r="K7">
-        <v>-0.6450333462394773</v>
+        <v>-0.2938650216339522</v>
       </c>
       <c r="L7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
         <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E8">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F8">
-        <v>5.501499320232195</v>
+        <v>5.031241254276178</v>
       </c>
       <c r="G8">
-        <v>2.121023700020244</v>
+        <v>2.31481099839796</v>
       </c>
       <c r="H8">
-        <v>2.59379436457013</v>
+        <v>2.173499805279226</v>
       </c>
       <c r="I8">
-        <v>0.01493073044433937</v>
+        <v>0.03640018383724646</v>
       </c>
       <c r="J8">
-        <v>1.156779225193753</v>
+        <v>0.3365869550217075</v>
       </c>
       <c r="K8">
-        <v>9.846219415270639</v>
+        <v>9.725895553530648</v>
       </c>
       <c r="L8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
       </c>
       <c r="O8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
         <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E9">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F9">
-        <v>-4.810789706071763</v>
+        <v>1.173858948624775</v>
       </c>
       <c r="G9">
-        <v>3.124924900168364</v>
+        <v>1.176467764706411</v>
       </c>
       <c r="H9">
-        <v>-1.539489702876561</v>
+        <v>0.9977825010086134</v>
       </c>
       <c r="I9">
-        <v>0.1367668029302571</v>
+        <v>0.3258704733857979</v>
       </c>
       <c r="J9">
-        <v>-11.26031771272485</v>
+        <v>-1.222527468811686</v>
       </c>
       <c r="K9">
-        <v>1.638738300581324</v>
+        <v>3.570245366061236</v>
       </c>
       <c r="L9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M9" t="s">
         <v>23</v>
@@ -2308,233 +2311,233 @@
         <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
         <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E10">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F10">
-        <v>5.246812088337475</v>
+        <v>-18.39049372851199</v>
       </c>
       <c r="G10">
-        <v>34.60602080118172</v>
+        <v>18.62767726252563</v>
       </c>
       <c r="H10">
-        <v>0.1516155850012755</v>
+        <v>-0.9872671439025419</v>
       </c>
       <c r="I10">
-        <v>0.8807574184531457</v>
+        <v>0.3309182655266213</v>
       </c>
       <c r="J10">
-        <v>-66.176504466891</v>
+        <v>-56.33383065576403</v>
       </c>
       <c r="K10">
-        <v>76.67012864356596</v>
+        <v>19.55284319874004</v>
       </c>
       <c r="L10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
       </c>
       <c r="O10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
         <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E11">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F11">
-        <v>36.93763645779599</v>
+        <v>16.38933540866935</v>
       </c>
       <c r="G11">
-        <v>34.06728847980239</v>
+        <v>17.10225365350495</v>
       </c>
       <c r="H11">
-        <v>1.084255252063731</v>
+        <v>0.9583143684288947</v>
       </c>
       <c r="I11">
-        <v>0.2890240288797525</v>
+        <v>0.3450891890973711</v>
       </c>
       <c r="J11">
-        <v>-33.37379123423516</v>
+        <v>-18.44681530646722</v>
       </c>
       <c r="K11">
-        <v>107.2490641498271</v>
+        <v>51.22548612380593</v>
       </c>
       <c r="L11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N11" t="b">
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12">
+        <v>44</v>
+      </c>
+      <c r="F12">
+        <v>-3.427761247987785</v>
+      </c>
+      <c r="G12">
+        <v>4.639192697641</v>
+      </c>
+      <c r="H12">
+        <v>-0.7388702025097557</v>
+      </c>
+      <c r="I12">
+        <v>0.4653711653327351</v>
+      </c>
+      <c r="J12">
+        <v>-12.87748754054935</v>
+      </c>
+      <c r="K12">
+        <v>6.021965044573784</v>
+      </c>
+      <c r="L12" t="s">
+        <v>97</v>
+      </c>
+      <c r="M12" t="s">
         <v>103</v>
-      </c>
-      <c r="C12" t="s">
-        <v>104</v>
-      </c>
-      <c r="D12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12">
-        <v>36</v>
-      </c>
-      <c r="F12">
-        <v>2.598237833638032</v>
-      </c>
-      <c r="G12">
-        <v>8.638369475890512</v>
-      </c>
-      <c r="H12">
-        <v>0.3007787338675028</v>
-      </c>
-      <c r="I12">
-        <v>0.7661734859586893</v>
-      </c>
-      <c r="J12">
-        <v>-15.23048050246384</v>
-      </c>
-      <c r="K12">
-        <v>20.4269561697399</v>
-      </c>
-      <c r="L12" t="s">
-        <v>99</v>
-      </c>
-      <c r="M12" t="s">
-        <v>105</v>
       </c>
       <c r="N12" t="b">
         <v>0</v>
       </c>
       <c r="O12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13">
+        <v>44</v>
+      </c>
+      <c r="F13">
+        <v>2.276086490724138</v>
+      </c>
+      <c r="G13">
+        <v>4.068293636107722</v>
+      </c>
+      <c r="H13">
+        <v>0.5594695698764137</v>
+      </c>
+      <c r="I13">
+        <v>0.5797364699158184</v>
+      </c>
+      <c r="J13">
+        <v>-6.010756467650218</v>
+      </c>
+      <c r="K13">
+        <v>10.56292944909849</v>
+      </c>
+      <c r="L13" t="s">
+        <v>97</v>
+      </c>
+      <c r="M13" t="s">
         <v>107</v>
-      </c>
-      <c r="C13" t="s">
-        <v>108</v>
-      </c>
-      <c r="D13" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13">
-        <v>36</v>
-      </c>
-      <c r="F13">
-        <v>7.922180092353511</v>
-      </c>
-      <c r="G13">
-        <v>8.5945906159867</v>
-      </c>
-      <c r="H13">
-        <v>0.921763519209112</v>
-      </c>
-      <c r="I13">
-        <v>0.3658257841077955</v>
-      </c>
-      <c r="J13">
-        <v>-9.816183117763163</v>
-      </c>
-      <c r="K13">
-        <v>25.66054330247018</v>
-      </c>
-      <c r="L13" t="s">
-        <v>99</v>
-      </c>
-      <c r="M13" t="s">
-        <v>109</v>
       </c>
       <c r="N13" t="b">
         <v>0</v>
       </c>
       <c r="O13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
         <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E14">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F14">
-        <v>-3.234287117971579</v>
+        <v>0.4679172092128251</v>
       </c>
       <c r="G14">
-        <v>4.680851127814104</v>
+        <v>1.401844266446955</v>
       </c>
       <c r="H14">
-        <v>-0.6909613293943722</v>
+        <v>0.3337868694921333</v>
       </c>
       <c r="I14">
-        <v>0.5017421224982936</v>
+        <v>0.7418504996962729</v>
       </c>
       <c r="J14">
-        <v>-13.34665118006968</v>
+        <v>-2.447377535442381</v>
       </c>
       <c r="K14">
-        <v>6.878076944126519</v>
+        <v>3.383211953868032</v>
       </c>
       <c r="L14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M14" t="s">
         <v>23</v>
@@ -2543,336 +2546,336 @@
         <v>0</v>
       </c>
       <c r="O14" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
         <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E15">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F15">
-        <v>0.9057264693775823</v>
+        <v>-12.52056622164889</v>
       </c>
       <c r="G15">
-        <v>33.98975385954066</v>
+        <v>18.81097600046333</v>
       </c>
       <c r="H15">
-        <v>0.02664704408041342</v>
+        <v>-0.6655989684607801</v>
       </c>
       <c r="I15">
-        <v>0.9791459640503541</v>
+        <v>0.5129126457367206</v>
       </c>
       <c r="J15">
-        <v>-72.52467240965927</v>
+        <v>-51.64013234505256</v>
       </c>
       <c r="K15">
-        <v>74.33612534841444</v>
+        <v>26.59899990175479</v>
       </c>
       <c r="L15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N15" t="b">
         <v>0</v>
       </c>
       <c r="O15" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
         <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E16">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F16">
-        <v>53.24399409703744</v>
+        <v>16.02001886221415</v>
       </c>
       <c r="G16">
-        <v>50.81885719979571</v>
+        <v>18.66881665859404</v>
       </c>
       <c r="H16">
-        <v>1.047721200964973</v>
+        <v>0.8581164599331721</v>
       </c>
       <c r="I16">
-        <v>0.3138565246061172</v>
+        <v>0.4005165596768037</v>
       </c>
       <c r="J16">
-        <v>-56.5434721546597</v>
+        <v>-22.80391072568077</v>
       </c>
       <c r="K16">
-        <v>163.0314603487346</v>
+        <v>54.84394845010907</v>
       </c>
       <c r="L16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N16" t="b">
         <v>0</v>
       </c>
       <c r="O16" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17">
+        <v>39</v>
+      </c>
+      <c r="F17">
+        <v>-2.311252122048333</v>
+      </c>
+      <c r="G17">
+        <v>4.710926755244442</v>
+      </c>
+      <c r="H17">
+        <v>-0.4906151681248982</v>
+      </c>
+      <c r="I17">
+        <v>0.6287860274746272</v>
+      </c>
+      <c r="J17">
+        <v>-12.10816062375272</v>
+      </c>
+      <c r="K17">
+        <v>7.485656379656056</v>
+      </c>
+      <c r="L17" t="s">
+        <v>110</v>
+      </c>
+      <c r="M17" t="s">
         <v>103</v>
-      </c>
-      <c r="C17" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17" t="s">
-        <v>84</v>
-      </c>
-      <c r="E17">
-        <v>31</v>
-      </c>
-      <c r="F17">
-        <v>1.666536266210316</v>
-      </c>
-      <c r="G17">
-        <v>8.485020431287293</v>
-      </c>
-      <c r="H17">
-        <v>0.1964092225476798</v>
-      </c>
-      <c r="I17">
-        <v>0.8473270090635971</v>
-      </c>
-      <c r="J17">
-        <v>-16.66423592298915</v>
-      </c>
-      <c r="K17">
-        <v>19.99730845540978</v>
-      </c>
-      <c r="L17" t="s">
-        <v>112</v>
-      </c>
-      <c r="M17" t="s">
-        <v>105</v>
       </c>
       <c r="N17" t="b">
         <v>0</v>
       </c>
       <c r="O17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18">
+        <v>39</v>
+      </c>
+      <c r="F18">
+        <v>1.865766725049547</v>
+      </c>
+      <c r="G18">
+        <v>4.468825485887885</v>
+      </c>
+      <c r="H18">
+        <v>0.4175071796697938</v>
+      </c>
+      <c r="I18">
+        <v>0.6805451637037974</v>
+      </c>
+      <c r="J18">
+        <v>-7.4276646250748</v>
+      </c>
+      <c r="K18">
+        <v>11.15919807517389</v>
+      </c>
+      <c r="L18" t="s">
+        <v>110</v>
+      </c>
+      <c r="M18" t="s">
         <v>107</v>
-      </c>
-      <c r="C18" t="s">
-        <v>108</v>
-      </c>
-      <c r="D18" t="s">
-        <v>84</v>
-      </c>
-      <c r="E18">
-        <v>31</v>
-      </c>
-      <c r="F18">
-        <v>11.69747045481679</v>
-      </c>
-      <c r="G18">
-        <v>12.52919560366158</v>
-      </c>
-      <c r="H18">
-        <v>0.9336170353504805</v>
-      </c>
-      <c r="I18">
-        <v>0.3675189358654612</v>
-      </c>
-      <c r="J18">
-        <v>-15.37021101802509</v>
-      </c>
-      <c r="K18">
-        <v>38.76515192765867</v>
-      </c>
-      <c r="L18" t="s">
-        <v>112</v>
-      </c>
-      <c r="M18" t="s">
-        <v>109</v>
       </c>
       <c r="N18" t="b">
         <v>0</v>
       </c>
       <c r="O18" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D19" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19">
+        <v>39</v>
+      </c>
+      <c r="F19">
+        <v>-0.4154772319729836</v>
+      </c>
+      <c r="G19">
+        <v>1.701461727756765</v>
+      </c>
+      <c r="H19">
+        <v>-0.2441884088223104</v>
+      </c>
+      <c r="I19">
+        <v>0.8094548345042303</v>
+      </c>
+      <c r="J19">
+        <v>-3.953860597290232</v>
+      </c>
+      <c r="K19">
+        <v>3.122906133344264</v>
+      </c>
+      <c r="L19" t="s">
+        <v>110</v>
+      </c>
+      <c r="M19" t="s">
         <v>118</v>
-      </c>
-      <c r="C19" t="s">
-        <v>119</v>
-      </c>
-      <c r="D19" t="s">
-        <v>84</v>
-      </c>
-      <c r="E19">
-        <v>31</v>
-      </c>
-      <c r="F19">
-        <v>0.2562013601435249</v>
-      </c>
-      <c r="G19">
-        <v>1.514519812481349</v>
-      </c>
-      <c r="H19">
-        <v>0.1691634259467173</v>
-      </c>
-      <c r="I19">
-        <v>0.8682719415744495</v>
-      </c>
-      <c r="J19">
-        <v>-3.015719772333088</v>
-      </c>
-      <c r="K19">
-        <v>3.528122492620137</v>
-      </c>
-      <c r="L19" t="s">
-        <v>112</v>
-      </c>
-      <c r="M19" t="s">
-        <v>120</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
       </c>
       <c r="O19" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C20" t="s">
+        <v>121</v>
+      </c>
+      <c r="D20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20">
+        <v>39</v>
+      </c>
+      <c r="F20">
+        <v>1.630325595356609</v>
+      </c>
+      <c r="G20">
+        <v>3.105037569521913</v>
+      </c>
+      <c r="H20">
+        <v>0.5250582509401432</v>
+      </c>
+      <c r="I20">
+        <v>0.6050424140701931</v>
+      </c>
+      <c r="J20">
+        <v>-4.826953522620746</v>
+      </c>
+      <c r="K20">
+        <v>8.087604713333965</v>
+      </c>
+      <c r="L20" t="s">
+        <v>110</v>
+      </c>
+      <c r="M20" t="s">
         <v>122</v>
-      </c>
-      <c r="C20" t="s">
-        <v>123</v>
-      </c>
-      <c r="D20" t="s">
-        <v>84</v>
-      </c>
-      <c r="E20">
-        <v>31</v>
-      </c>
-      <c r="F20">
-        <v>-0.8585883127407358</v>
-      </c>
-      <c r="G20">
-        <v>3.168911666660741</v>
-      </c>
-      <c r="H20">
-        <v>-0.2709410684348542</v>
-      </c>
-      <c r="I20">
-        <v>0.7906906588498602</v>
-      </c>
-      <c r="J20">
-        <v>-7.704605752493866</v>
-      </c>
-      <c r="K20">
-        <v>5.987429127012395</v>
-      </c>
-      <c r="L20" t="s">
-        <v>112</v>
-      </c>
-      <c r="M20" t="s">
-        <v>124</v>
       </c>
       <c r="N20" t="b">
         <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21">
+        <v>39</v>
+      </c>
+      <c r="F21">
+        <v>0.03081430078259972</v>
+      </c>
+      <c r="G21">
+        <v>0.06754827568609117</v>
+      </c>
+      <c r="H21">
+        <v>0.456181900568406</v>
+      </c>
+      <c r="I21">
+        <v>0.652941871074479</v>
+      </c>
+      <c r="J21">
+        <v>-0.1096600285216776</v>
+      </c>
+      <c r="K21">
+        <v>0.1712886300868771</v>
+      </c>
+      <c r="L21" t="s">
+        <v>110</v>
+      </c>
+      <c r="M21" t="s">
         <v>126</v>
-      </c>
-      <c r="C21" t="s">
-        <v>127</v>
-      </c>
-      <c r="D21" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21">
-        <v>31</v>
-      </c>
-      <c r="F21">
-        <v>-0.05412327243670201</v>
-      </c>
-      <c r="G21">
-        <v>0.06027318568718423</v>
-      </c>
-      <c r="H21">
-        <v>-0.8979660162248589</v>
-      </c>
-      <c r="I21">
-        <v>0.385532919132147</v>
-      </c>
-      <c r="J21">
-        <v>-0.1843355736204566</v>
-      </c>
-      <c r="K21">
-        <v>0.07608902874705259</v>
-      </c>
-      <c r="L21" t="s">
-        <v>112</v>
-      </c>
-      <c r="M21" t="s">
-        <v>128</v>
       </c>
       <c r="N21" t="b">
         <v>0</v>
       </c>
       <c r="O21" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -2890,16 +2893,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>8</v>
@@ -2910,117 +2913,117 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>5.806236284200734</v>
+        <v>0.759571943172292</v>
       </c>
       <c r="F2">
-        <v>0.007386964173758466</v>
+        <v>0.4748378259244989</v>
       </c>
       <c r="G2" t="s">
-        <v>36</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E3">
-        <v>8.115896351486487</v>
+        <v>0.9167402567205372</v>
       </c>
       <c r="F3">
-        <v>0.001523027722757665</v>
+        <v>0.4084806478458676</v>
       </c>
       <c r="G3" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B4">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E4">
-        <v>8.599476119849234</v>
+        <v>2.201308263069723</v>
       </c>
       <c r="F4">
-        <v>0.0003324260727056167</v>
+        <v>0.1047438292094812</v>
       </c>
       <c r="G4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B5">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C5">
         <v>5</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>5.417474966421664</v>
+        <v>1.596308016863364</v>
       </c>
       <c r="F5">
-        <v>0.001788371524256679</v>
+        <v>0.1894070847567736</v>
       </c>
       <c r="G5" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B6">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C6">
         <v>8</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>3.45411170739337</v>
+        <v>1.418772967563044</v>
       </c>
       <c r="F6">
-        <v>0.02330375464484713</v>
+        <v>0.2460161410532619</v>
       </c>
       <c r="G6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -3035,23 +3038,23 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -3059,66 +3062,66 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
